--- a/uploads/voucher_prequest_SC2026081701.xlsx
+++ b/uploads/voucher_prequest_SC2026081701.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购申请单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物资采购申请单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62,32 +62,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,130 +452,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.1" customWidth="1" min="1" max="1"/>
+    <col width="10.9" customWidth="1" min="2" max="2"/>
+    <col width="24.6" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="4" max="4"/>
+    <col width="23.4" customWidth="1" min="5" max="5"/>
+    <col width="5.2" customWidth="1" min="6" max="6"/>
+    <col width="8.199999999999999" customWidth="1" min="7" max="7"/>
+    <col width="17.2" customWidth="1" min="8" max="8"/>
+    <col width="10.2" customWidth="1" min="9" max="9"/>
+    <col width="7.3" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>采购申请单</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>物资采购申请单
+ 申请部门：维修车间        申请日期：2026年8月17日        编号：SC2026081701</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>单号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>SC2026081701</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>申请部门</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>维修车间</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>申请人</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>邢果</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>采购类别</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>物品名称</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>厂家/品牌/技术参数</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>规格型号</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>到货日期</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>请购数量</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>采购事由</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>经办人：                        部门负责人：</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>预计金额</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>¥0.00</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>已通过</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>计划采购负责人：                         采购员：</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>经手人：                验收人：                审批人：</t>
-        </is>
-      </c>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B8:F8"/>
+  <mergeCells count="3">
+    <mergeCell ref="A8:L10"/>
+    <mergeCell ref="A6:L7"/>
+    <mergeCell ref="A1:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>